--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_20_35.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_20_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1339975.48604722</v>
+        <v>1344407.3818491</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5413711.842035519</v>
+        <v>5413711.842050619</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11200271.94323291</v>
+        <v>11192483.67277902</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6679779.616944303</v>
+        <v>6680756.832636416</v>
       </c>
     </row>
     <row r="11">
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.396370515167757e-07</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -5103,13 +5103,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.385475267846219e-07</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.385475267846219e-07</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.385475267846219e-07</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>142.1340340644906</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
@@ -23215,31 +23215,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>371.7338416634806</v>
+        <v>370.7845523088681</v>
       </c>
       <c r="C11" t="n">
-        <v>354.2728917710076</v>
+        <v>353.323602416395</v>
       </c>
       <c r="D11" t="n">
-        <v>343.683041620683</v>
+        <v>342.7337522660704</v>
       </c>
       <c r="E11" t="n">
-        <v>370.9303700722618</v>
+        <v>369.9810807176493</v>
       </c>
       <c r="F11" t="n">
-        <v>395.8760457417114</v>
+        <v>394.9267563870989</v>
       </c>
       <c r="G11" t="n">
-        <v>404.302737515135</v>
+        <v>403.3534481605225</v>
       </c>
       <c r="H11" t="n">
-        <v>328.4748021157671</v>
+        <v>327.5255127611546</v>
       </c>
       <c r="I11" t="n">
-        <v>199.4758895704059</v>
+        <v>198.5266002157934</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9492893546125174</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>138.8691179411497</v>
+        <v>137.9198285865372</v>
       </c>
       <c r="S11" t="n">
-        <v>198.0200695862453</v>
+        <v>197.0707802316328</v>
       </c>
       <c r="T11" t="n">
-        <v>212.0958495641314</v>
+        <v>211.1465602095188</v>
       </c>
       <c r="U11" t="n">
-        <v>240.3456529078365</v>
+        <v>239.396363553224</v>
       </c>
       <c r="V11" t="n">
-        <v>316.7522584701349</v>
+        <v>315.8029691155224</v>
       </c>
       <c r="W11" t="n">
-        <v>338.240968717413</v>
+        <v>337.2916793628005</v>
       </c>
       <c r="X11" t="n">
-        <v>358.731100678469</v>
+        <v>357.7818113238565</v>
       </c>
       <c r="Y11" t="n">
-        <v>375.2379386560536</v>
+        <v>374.2886493014411</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155.5331836498673</v>
+        <v>154.5838942952548</v>
       </c>
       <c r="C12" t="n">
-        <v>161.7084989883157</v>
+        <v>160.7592096337032</v>
       </c>
       <c r="D12" t="n">
-        <v>136.4450655646388</v>
+        <v>135.4957762100262</v>
       </c>
       <c r="E12" t="n">
-        <v>146.6450804554009</v>
+        <v>145.6957911007884</v>
       </c>
       <c r="F12" t="n">
-        <v>134.0692123933839</v>
+        <v>133.1199230387714</v>
       </c>
       <c r="G12" t="n">
-        <v>126.3435171632106</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="H12" t="n">
-        <v>101.2354442364965</v>
+        <v>100.2861548818839</v>
       </c>
       <c r="I12" t="n">
-        <v>78.39663285141508</v>
+        <v>77.44734349680256</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>89.15783415264313</v>
+        <v>88.20854479803062</v>
       </c>
       <c r="S12" t="n">
-        <v>160.6831711038378</v>
+        <v>159.7338817492253</v>
       </c>
       <c r="T12" t="n">
-        <v>189.1647286948216</v>
+        <v>188.2154393402091</v>
       </c>
       <c r="U12" t="n">
-        <v>214.9413820809748</v>
+        <v>213.9920927263623</v>
       </c>
       <c r="V12" t="n">
-        <v>221.8005871494253</v>
+        <v>220.8512977948128</v>
       </c>
       <c r="W12" t="n">
-        <v>240.6949831609196</v>
+        <v>239.7456938063071</v>
       </c>
       <c r="X12" t="n">
-        <v>194.7729852034775</v>
+        <v>193.823695848865</v>
       </c>
       <c r="Y12" t="n">
-        <v>194.6826957773044</v>
+        <v>193.7334064226918</v>
       </c>
     </row>
     <row r="13">
@@ -23373,34 +23373,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>168.8319801819373</v>
+        <v>167.8826908273248</v>
       </c>
       <c r="C13" t="n">
-        <v>156.2468210986278</v>
+        <v>155.2975317440153</v>
       </c>
       <c r="D13" t="n">
-        <v>137.6154730182124</v>
+        <v>136.6661836635998</v>
       </c>
       <c r="E13" t="n">
-        <v>135.4339626465692</v>
+        <v>134.4846732919567</v>
       </c>
       <c r="F13" t="n">
-        <v>134.4210480229312</v>
+        <v>133.4717586683187</v>
       </c>
       <c r="G13" t="n">
-        <v>156.9909793584588</v>
+        <v>156.0416900038462</v>
       </c>
       <c r="H13" t="n">
-        <v>151.2271725074396</v>
+        <v>150.2778831528271</v>
       </c>
       <c r="I13" t="n">
-        <v>144.4504749272583</v>
+        <v>143.5011855726458</v>
       </c>
       <c r="J13" t="n">
-        <v>82.35918011667277</v>
+        <v>81.40989076206026</v>
       </c>
       <c r="K13" t="n">
-        <v>11.26949182588285</v>
+        <v>10.32020247127033</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>75.16204325169439</v>
+        <v>74.21275389708187</v>
       </c>
       <c r="R13" t="n">
-        <v>166.2933913771695</v>
+        <v>165.344102022557</v>
       </c>
       <c r="S13" t="n">
-        <v>213.0165980369723</v>
+        <v>212.0673086823597</v>
       </c>
       <c r="T13" t="n">
-        <v>216.9455894282815</v>
+        <v>215.996300073669</v>
       </c>
       <c r="U13" t="n">
-        <v>275.3190293564909</v>
+        <v>274.3697400018784</v>
       </c>
       <c r="V13" t="n">
-        <v>241.137643323828</v>
+        <v>240.1883539692155</v>
       </c>
       <c r="W13" t="n">
-        <v>275.522998336591</v>
+        <v>274.5737089819785</v>
       </c>
       <c r="X13" t="n">
-        <v>214.7096553890372</v>
+        <v>213.7603660344246</v>
       </c>
       <c r="Y13" t="n">
-        <v>207.5846533520948</v>
+        <v>206.6353639974823</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>290.7338416634806</v>
+        <v>291.4725427837783</v>
       </c>
       <c r="C14" t="n">
-        <v>273.2728917710076</v>
+        <v>274.0115928913053</v>
       </c>
       <c r="D14" t="n">
-        <v>262.683041620683</v>
+        <v>263.4217427409807</v>
       </c>
       <c r="E14" t="n">
-        <v>289.9303700722618</v>
+        <v>290.6690711925595</v>
       </c>
       <c r="F14" t="n">
-        <v>314.8760457417114</v>
+        <v>315.6147468620092</v>
       </c>
       <c r="G14" t="n">
-        <v>323.302737515135</v>
+        <v>324.0414386354328</v>
       </c>
       <c r="H14" t="n">
-        <v>247.4748021157671</v>
+        <v>248.2135032360649</v>
       </c>
       <c r="I14" t="n">
-        <v>118.4758895704059</v>
+        <v>119.2145906907037</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>57.86911794114968</v>
+        <v>58.60781906144743</v>
       </c>
       <c r="S14" t="n">
-        <v>117.0200695862453</v>
+        <v>117.7587707065431</v>
       </c>
       <c r="T14" t="n">
-        <v>131.0958495641314</v>
+        <v>131.8345506844291</v>
       </c>
       <c r="U14" t="n">
-        <v>159.3456529078365</v>
+        <v>160.0843540281342</v>
       </c>
       <c r="V14" t="n">
-        <v>235.7522584701349</v>
+        <v>236.4909595904327</v>
       </c>
       <c r="W14" t="n">
-        <v>257.240968717413</v>
+        <v>257.9796698377107</v>
       </c>
       <c r="X14" t="n">
-        <v>277.731100678469</v>
+        <v>278.4698017987668</v>
       </c>
       <c r="Y14" t="n">
-        <v>294.2379386560536</v>
+        <v>294.9766397763514</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>74.53318364986734</v>
+        <v>75.27188477016509</v>
       </c>
       <c r="C15" t="n">
-        <v>80.70849898831574</v>
+        <v>81.44720010861349</v>
       </c>
       <c r="D15" t="n">
-        <v>55.44506556463875</v>
+        <v>56.1837666849365</v>
       </c>
       <c r="E15" t="n">
-        <v>65.64508045540094</v>
+        <v>66.38378157569869</v>
       </c>
       <c r="F15" t="n">
-        <v>53.06921239338388</v>
+        <v>53.80791351368163</v>
       </c>
       <c r="G15" t="n">
-        <v>45.34351716321063</v>
+        <v>46.08221828350838</v>
       </c>
       <c r="H15" t="n">
-        <v>20.23544423649646</v>
+        <v>20.97414535679421</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>8.157834152643133</v>
+        <v>8.896535272940881</v>
       </c>
       <c r="S15" t="n">
-        <v>79.68317110383782</v>
+        <v>80.42187222413557</v>
       </c>
       <c r="T15" t="n">
-        <v>108.1647286948216</v>
+        <v>108.9034298151194</v>
       </c>
       <c r="U15" t="n">
-        <v>133.9413820809748</v>
+        <v>134.6800832012726</v>
       </c>
       <c r="V15" t="n">
-        <v>140.8005871494253</v>
+        <v>141.539288269723</v>
       </c>
       <c r="W15" t="n">
-        <v>159.6949831609196</v>
+        <v>160.4336842812174</v>
       </c>
       <c r="X15" t="n">
-        <v>113.7729852034775</v>
+        <v>114.5116863237752</v>
       </c>
       <c r="Y15" t="n">
-        <v>113.6826957773044</v>
+        <v>114.4213968976021</v>
       </c>
     </row>
     <row r="16">
@@ -23610,31 +23610,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87.8319801819373</v>
+        <v>88.57068130223504</v>
       </c>
       <c r="C16" t="n">
-        <v>75.24682109862783</v>
+        <v>75.98552221892558</v>
       </c>
       <c r="D16" t="n">
-        <v>56.61547301821236</v>
+        <v>57.3541741385101</v>
       </c>
       <c r="E16" t="n">
-        <v>54.43396264656917</v>
+        <v>55.17266376686692</v>
       </c>
       <c r="F16" t="n">
-        <v>53.42104802293125</v>
+        <v>54.15974914322899</v>
       </c>
       <c r="G16" t="n">
-        <v>75.99097935845876</v>
+        <v>76.72968047875651</v>
       </c>
       <c r="H16" t="n">
-        <v>70.22717250743958</v>
+        <v>70.96587362773732</v>
       </c>
       <c r="I16" t="n">
-        <v>63.45047492725828</v>
+        <v>64.18917604755603</v>
       </c>
       <c r="J16" t="n">
-        <v>1.359180116672775</v>
+        <v>2.097881236970522</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>85.29339137716948</v>
+        <v>86.03209249746723</v>
       </c>
       <c r="S16" t="n">
-        <v>132.0165980369723</v>
+        <v>132.75529915727</v>
       </c>
       <c r="T16" t="n">
-        <v>135.9455894282815</v>
+        <v>136.6842905485792</v>
       </c>
       <c r="U16" t="n">
-        <v>194.3190293564909</v>
+        <v>195.0577304767886</v>
       </c>
       <c r="V16" t="n">
-        <v>160.137643323828</v>
+        <v>160.8763444441257</v>
       </c>
       <c r="W16" t="n">
-        <v>194.522998336591</v>
+        <v>195.2616994568887</v>
       </c>
       <c r="X16" t="n">
-        <v>133.7096553890372</v>
+        <v>134.4483565093349</v>
       </c>
       <c r="Y16" t="n">
-        <v>126.5846533520948</v>
+        <v>127.3233544723925</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>290.7338416634806</v>
+        <v>291.4725427837783</v>
       </c>
       <c r="C17" t="n">
-        <v>273.2728917710076</v>
+        <v>274.0115928913053</v>
       </c>
       <c r="D17" t="n">
-        <v>262.683041620683</v>
+        <v>263.4217427409807</v>
       </c>
       <c r="E17" t="n">
-        <v>289.9303700722618</v>
+        <v>290.6690711925595</v>
       </c>
       <c r="F17" t="n">
-        <v>314.8760457417114</v>
+        <v>315.6147468620092</v>
       </c>
       <c r="G17" t="n">
-        <v>323.302737515135</v>
+        <v>324.0414386354328</v>
       </c>
       <c r="H17" t="n">
-        <v>247.4748021157671</v>
+        <v>248.2135032360649</v>
       </c>
       <c r="I17" t="n">
-        <v>118.4758895704059</v>
+        <v>119.2145906907037</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>57.86911794114968</v>
+        <v>58.60781906144743</v>
       </c>
       <c r="S17" t="n">
-        <v>117.0200695862453</v>
+        <v>117.7587707065431</v>
       </c>
       <c r="T17" t="n">
-        <v>131.0958495641314</v>
+        <v>131.8345506844291</v>
       </c>
       <c r="U17" t="n">
-        <v>159.3456529078365</v>
+        <v>160.0843540281342</v>
       </c>
       <c r="V17" t="n">
-        <v>235.7522584701349</v>
+        <v>236.4909595904327</v>
       </c>
       <c r="W17" t="n">
-        <v>257.240968717413</v>
+        <v>257.9796698377107</v>
       </c>
       <c r="X17" t="n">
-        <v>277.731100678469</v>
+        <v>278.4698017987668</v>
       </c>
       <c r="Y17" t="n">
-        <v>294.2379386560536</v>
+        <v>294.9766397763514</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>74.53318364986734</v>
+        <v>75.27188477016509</v>
       </c>
       <c r="C18" t="n">
-        <v>80.70849898831574</v>
+        <v>81.44720010861349</v>
       </c>
       <c r="D18" t="n">
-        <v>55.44506556463875</v>
+        <v>56.1837666849365</v>
       </c>
       <c r="E18" t="n">
-        <v>65.64508045540094</v>
+        <v>66.38378157569869</v>
       </c>
       <c r="F18" t="n">
-        <v>53.06921239338388</v>
+        <v>53.80791351368163</v>
       </c>
       <c r="G18" t="n">
-        <v>45.34351716321063</v>
+        <v>46.08221828350838</v>
       </c>
       <c r="H18" t="n">
-        <v>20.23544423649646</v>
+        <v>20.97414535679421</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>8.157834152643133</v>
+        <v>8.896535272940881</v>
       </c>
       <c r="S18" t="n">
-        <v>79.68317110383782</v>
+        <v>80.42187222413557</v>
       </c>
       <c r="T18" t="n">
-        <v>108.1647286948216</v>
+        <v>108.9034298151194</v>
       </c>
       <c r="U18" t="n">
-        <v>133.9413820809748</v>
+        <v>134.6800832012726</v>
       </c>
       <c r="V18" t="n">
-        <v>140.8005871494253</v>
+        <v>141.539288269723</v>
       </c>
       <c r="W18" t="n">
-        <v>159.6949831609196</v>
+        <v>160.4336842812174</v>
       </c>
       <c r="X18" t="n">
-        <v>113.7729852034775</v>
+        <v>114.5116863237752</v>
       </c>
       <c r="Y18" t="n">
-        <v>113.6826957773044</v>
+        <v>114.4213968976021</v>
       </c>
     </row>
     <row r="19">
@@ -23847,31 +23847,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87.8319801819373</v>
+        <v>88.57068130223504</v>
       </c>
       <c r="C19" t="n">
-        <v>75.24682109862783</v>
+        <v>75.98552221892558</v>
       </c>
       <c r="D19" t="n">
-        <v>56.61547301821236</v>
+        <v>57.3541741385101</v>
       </c>
       <c r="E19" t="n">
-        <v>54.43396264656917</v>
+        <v>55.17266376686692</v>
       </c>
       <c r="F19" t="n">
-        <v>53.42104802293125</v>
+        <v>54.15974914322899</v>
       </c>
       <c r="G19" t="n">
-        <v>75.99097935845876</v>
+        <v>76.72968047875651</v>
       </c>
       <c r="H19" t="n">
-        <v>70.22717250743958</v>
+        <v>70.96587362773732</v>
       </c>
       <c r="I19" t="n">
-        <v>63.45047492725828</v>
+        <v>64.18917604755603</v>
       </c>
       <c r="J19" t="n">
-        <v>1.359180116672775</v>
+        <v>2.097881236970522</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>85.29339137716948</v>
+        <v>86.03209249746723</v>
       </c>
       <c r="S19" t="n">
-        <v>132.0165980369723</v>
+        <v>132.75529915727</v>
       </c>
       <c r="T19" t="n">
-        <v>135.9455894282815</v>
+        <v>136.6842905485792</v>
       </c>
       <c r="U19" t="n">
-        <v>194.3190293564909</v>
+        <v>195.0577304767886</v>
       </c>
       <c r="V19" t="n">
-        <v>160.137643323828</v>
+        <v>160.8763444441257</v>
       </c>
       <c r="W19" t="n">
-        <v>194.522998336591</v>
+        <v>195.2616994568887</v>
       </c>
       <c r="X19" t="n">
-        <v>133.7096553890372</v>
+        <v>134.4483565093349</v>
       </c>
       <c r="Y19" t="n">
-        <v>126.5846533520948</v>
+        <v>127.3233544723925</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>290.7338416634806</v>
+        <v>291.4725427837783</v>
       </c>
       <c r="C20" t="n">
-        <v>273.2728917710076</v>
+        <v>274.0115928913053</v>
       </c>
       <c r="D20" t="n">
-        <v>262.683041620683</v>
+        <v>263.4217427409807</v>
       </c>
       <c r="E20" t="n">
-        <v>289.9303700722618</v>
+        <v>290.6690711925595</v>
       </c>
       <c r="F20" t="n">
-        <v>314.8760457417114</v>
+        <v>315.6147468620092</v>
       </c>
       <c r="G20" t="n">
-        <v>323.302737515135</v>
+        <v>324.0414386354328</v>
       </c>
       <c r="H20" t="n">
-        <v>247.4748021157671</v>
+        <v>248.2135032360649</v>
       </c>
       <c r="I20" t="n">
-        <v>118.4758895704059</v>
+        <v>119.2145906907037</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>57.86911794114968</v>
+        <v>58.60781906144743</v>
       </c>
       <c r="S20" t="n">
-        <v>117.0200695862453</v>
+        <v>117.7587707065431</v>
       </c>
       <c r="T20" t="n">
-        <v>131.0958495641314</v>
+        <v>131.8345506844291</v>
       </c>
       <c r="U20" t="n">
-        <v>159.3456529078365</v>
+        <v>160.0843540281342</v>
       </c>
       <c r="V20" t="n">
-        <v>235.7522584701349</v>
+        <v>236.4909595904327</v>
       </c>
       <c r="W20" t="n">
-        <v>257.240968717413</v>
+        <v>257.9796698377107</v>
       </c>
       <c r="X20" t="n">
-        <v>277.731100678469</v>
+        <v>278.4698017987668</v>
       </c>
       <c r="Y20" t="n">
-        <v>294.2379386560536</v>
+        <v>294.9766397763514</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>74.53318364986734</v>
+        <v>75.27188477016509</v>
       </c>
       <c r="C21" t="n">
-        <v>80.70849898831574</v>
+        <v>81.44720010861349</v>
       </c>
       <c r="D21" t="n">
-        <v>55.44506556463875</v>
+        <v>56.1837666849365</v>
       </c>
       <c r="E21" t="n">
-        <v>65.64508045540094</v>
+        <v>66.38378157569869</v>
       </c>
       <c r="F21" t="n">
-        <v>53.06921239338388</v>
+        <v>53.80791351368163</v>
       </c>
       <c r="G21" t="n">
-        <v>45.34351716321063</v>
+        <v>46.08221828350838</v>
       </c>
       <c r="H21" t="n">
-        <v>20.23544423649646</v>
+        <v>20.97414535679421</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>8.157834152643133</v>
+        <v>8.896535272940881</v>
       </c>
       <c r="S21" t="n">
-        <v>79.68317110383782</v>
+        <v>80.42187222413557</v>
       </c>
       <c r="T21" t="n">
-        <v>108.1647286948216</v>
+        <v>108.9034298151194</v>
       </c>
       <c r="U21" t="n">
-        <v>133.9413820809748</v>
+        <v>134.6800832012726</v>
       </c>
       <c r="V21" t="n">
-        <v>140.8005871494253</v>
+        <v>141.539288269723</v>
       </c>
       <c r="W21" t="n">
-        <v>159.6949831609196</v>
+        <v>160.4336842812174</v>
       </c>
       <c r="X21" t="n">
-        <v>113.7729852034775</v>
+        <v>114.5116863237752</v>
       </c>
       <c r="Y21" t="n">
-        <v>113.6826957773044</v>
+        <v>114.4213968976021</v>
       </c>
     </row>
     <row r="22">
@@ -24084,31 +24084,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>87.8319801819373</v>
+        <v>88.57068130223504</v>
       </c>
       <c r="C22" t="n">
-        <v>75.24682109862783</v>
+        <v>75.98552221892558</v>
       </c>
       <c r="D22" t="n">
-        <v>56.61547301821236</v>
+        <v>57.3541741385101</v>
       </c>
       <c r="E22" t="n">
-        <v>54.43396264656917</v>
+        <v>55.17266376686692</v>
       </c>
       <c r="F22" t="n">
-        <v>53.42104802293125</v>
+        <v>54.15974914322899</v>
       </c>
       <c r="G22" t="n">
-        <v>75.99097935845876</v>
+        <v>76.72968047875651</v>
       </c>
       <c r="H22" t="n">
-        <v>70.22717250743958</v>
+        <v>70.96587362773732</v>
       </c>
       <c r="I22" t="n">
-        <v>63.45047492725828</v>
+        <v>64.18917604755603</v>
       </c>
       <c r="J22" t="n">
-        <v>1.359180116672775</v>
+        <v>2.097881236970522</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>85.29339137716948</v>
+        <v>86.03209249746723</v>
       </c>
       <c r="S22" t="n">
-        <v>132.0165980369723</v>
+        <v>132.75529915727</v>
       </c>
       <c r="T22" t="n">
-        <v>135.9455894282815</v>
+        <v>136.6842905485792</v>
       </c>
       <c r="U22" t="n">
-        <v>194.3190293564909</v>
+        <v>195.0577304767886</v>
       </c>
       <c r="V22" t="n">
-        <v>160.137643323828</v>
+        <v>160.8763444441257</v>
       </c>
       <c r="W22" t="n">
-        <v>194.522998336591</v>
+        <v>195.2616994568887</v>
       </c>
       <c r="X22" t="n">
-        <v>133.7096553890372</v>
+        <v>134.4483565093349</v>
       </c>
       <c r="Y22" t="n">
-        <v>126.5846533520948</v>
+        <v>127.3233544723925</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>290.7338416634806</v>
+        <v>291.4725427837783</v>
       </c>
       <c r="C23" t="n">
-        <v>273.2728917710076</v>
+        <v>274.0115928913053</v>
       </c>
       <c r="D23" t="n">
-        <v>262.683041620683</v>
+        <v>263.4217427409807</v>
       </c>
       <c r="E23" t="n">
-        <v>289.9303700722618</v>
+        <v>290.6690711925595</v>
       </c>
       <c r="F23" t="n">
-        <v>314.8760457417114</v>
+        <v>315.6147468620092</v>
       </c>
       <c r="G23" t="n">
-        <v>323.302737515135</v>
+        <v>324.0414386354328</v>
       </c>
       <c r="H23" t="n">
-        <v>247.4748021157671</v>
+        <v>248.2135032360649</v>
       </c>
       <c r="I23" t="n">
-        <v>118.4758895704059</v>
+        <v>119.2145906907037</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>57.86911794114968</v>
+        <v>58.60781906144743</v>
       </c>
       <c r="S23" t="n">
-        <v>117.0200695862453</v>
+        <v>117.7587707065431</v>
       </c>
       <c r="T23" t="n">
-        <v>131.0958495641314</v>
+        <v>131.8345506844291</v>
       </c>
       <c r="U23" t="n">
-        <v>159.3456529078365</v>
+        <v>160.0843540281342</v>
       </c>
       <c r="V23" t="n">
-        <v>235.7522584701349</v>
+        <v>236.4909595904327</v>
       </c>
       <c r="W23" t="n">
-        <v>257.240968717413</v>
+        <v>257.9796698377107</v>
       </c>
       <c r="X23" t="n">
-        <v>277.731100678469</v>
+        <v>278.4698017987668</v>
       </c>
       <c r="Y23" t="n">
-        <v>294.2379386560536</v>
+        <v>294.9766397763514</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>74.53318364986734</v>
+        <v>75.27188477016509</v>
       </c>
       <c r="C24" t="n">
-        <v>80.70849898831574</v>
+        <v>81.44720010861349</v>
       </c>
       <c r="D24" t="n">
-        <v>55.44506556463875</v>
+        <v>56.1837666849365</v>
       </c>
       <c r="E24" t="n">
-        <v>65.64508045540094</v>
+        <v>66.38378157569869</v>
       </c>
       <c r="F24" t="n">
-        <v>53.06921239338388</v>
+        <v>53.80791351368163</v>
       </c>
       <c r="G24" t="n">
-        <v>45.34351716321063</v>
+        <v>46.08221828350838</v>
       </c>
       <c r="H24" t="n">
-        <v>20.23544423649646</v>
+        <v>20.97414535679421</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>8.157834152643133</v>
+        <v>8.896535272940881</v>
       </c>
       <c r="S24" t="n">
-        <v>79.68317110383782</v>
+        <v>80.42187222413557</v>
       </c>
       <c r="T24" t="n">
-        <v>108.1647286948216</v>
+        <v>108.9034298151194</v>
       </c>
       <c r="U24" t="n">
-        <v>133.9413820809748</v>
+        <v>134.6800832012726</v>
       </c>
       <c r="V24" t="n">
-        <v>140.8005871494253</v>
+        <v>141.539288269723</v>
       </c>
       <c r="W24" t="n">
-        <v>159.6949831609196</v>
+        <v>160.4336842812174</v>
       </c>
       <c r="X24" t="n">
-        <v>113.7729852034775</v>
+        <v>114.5116863237752</v>
       </c>
       <c r="Y24" t="n">
-        <v>113.6826957773044</v>
+        <v>114.4213968976021</v>
       </c>
     </row>
     <row r="25">
@@ -24321,31 +24321,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>87.8319801819373</v>
+        <v>88.57068130223504</v>
       </c>
       <c r="C25" t="n">
-        <v>75.24682109862783</v>
+        <v>75.98552221892558</v>
       </c>
       <c r="D25" t="n">
-        <v>56.61547301821236</v>
+        <v>57.3541741385101</v>
       </c>
       <c r="E25" t="n">
-        <v>54.43396264656917</v>
+        <v>55.17266376686692</v>
       </c>
       <c r="F25" t="n">
-        <v>53.42104802293125</v>
+        <v>54.15974914322899</v>
       </c>
       <c r="G25" t="n">
-        <v>75.99097935845876</v>
+        <v>76.72968047875651</v>
       </c>
       <c r="H25" t="n">
-        <v>70.22717250743958</v>
+        <v>70.96587362773732</v>
       </c>
       <c r="I25" t="n">
-        <v>63.45047492725828</v>
+        <v>64.18917604755603</v>
       </c>
       <c r="J25" t="n">
-        <v>1.359180116672775</v>
+        <v>2.097881236970522</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>85.29339137716948</v>
+        <v>86.03209249746723</v>
       </c>
       <c r="S25" t="n">
-        <v>132.0165980369723</v>
+        <v>132.75529915727</v>
       </c>
       <c r="T25" t="n">
-        <v>135.9455894282815</v>
+        <v>136.6842905485792</v>
       </c>
       <c r="U25" t="n">
-        <v>194.3190293564909</v>
+        <v>195.0577304767886</v>
       </c>
       <c r="V25" t="n">
-        <v>160.137643323828</v>
+        <v>160.8763444441257</v>
       </c>
       <c r="W25" t="n">
-        <v>194.522998336591</v>
+        <v>195.2616994568887</v>
       </c>
       <c r="X25" t="n">
-        <v>133.7096553890372</v>
+        <v>134.4483565093349</v>
       </c>
       <c r="Y25" t="n">
-        <v>126.5846533520948</v>
+        <v>127.3233544723925</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>293.7338416634806</v>
+        <v>295.6961369082176</v>
       </c>
       <c r="C26" t="n">
-        <v>276.2728917710076</v>
+        <v>278.2351870157446</v>
       </c>
       <c r="D26" t="n">
-        <v>265.683041620683</v>
+        <v>267.6453368654199</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9303700722618</v>
+        <v>294.8926653169988</v>
       </c>
       <c r="F26" t="n">
-        <v>317.8760457417114</v>
+        <v>319.8383409864484</v>
       </c>
       <c r="G26" t="n">
-        <v>326.302737515135</v>
+        <v>328.265032759872</v>
       </c>
       <c r="H26" t="n">
-        <v>250.4748021157671</v>
+        <v>252.4370973605042</v>
       </c>
       <c r="I26" t="n">
-        <v>121.4758895704059</v>
+        <v>123.4381848151429</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>60.86911794114968</v>
+        <v>62.8314131858867</v>
       </c>
       <c r="S26" t="n">
-        <v>120.0200695862453</v>
+        <v>121.9823648309824</v>
       </c>
       <c r="T26" t="n">
-        <v>134.0958495641314</v>
+        <v>136.0581448088684</v>
       </c>
       <c r="U26" t="n">
-        <v>162.3456529078365</v>
+        <v>164.3079481525735</v>
       </c>
       <c r="V26" t="n">
-        <v>238.7522584701349</v>
+        <v>240.7145537148719</v>
       </c>
       <c r="W26" t="n">
-        <v>260.240968717413</v>
+        <v>262.20326396215</v>
       </c>
       <c r="X26" t="n">
-        <v>280.731100678469</v>
+        <v>282.693395923206</v>
       </c>
       <c r="Y26" t="n">
-        <v>297.2379386560536</v>
+        <v>299.2002339007906</v>
       </c>
     </row>
     <row r="27">
@@ -24479,28 +24479,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77.53318364986734</v>
+        <v>79.49547889460436</v>
       </c>
       <c r="C27" t="n">
-        <v>83.70849898831574</v>
+        <v>85.67079423305276</v>
       </c>
       <c r="D27" t="n">
-        <v>58.44506556463875</v>
+        <v>60.40736080937577</v>
       </c>
       <c r="E27" t="n">
-        <v>68.64508045540094</v>
+        <v>70.60737570013796</v>
       </c>
       <c r="F27" t="n">
-        <v>56.06921239338388</v>
+        <v>58.0315076381209</v>
       </c>
       <c r="G27" t="n">
-        <v>48.34351716321063</v>
+        <v>50.30581240794766</v>
       </c>
       <c r="H27" t="n">
-        <v>23.23544423649646</v>
+        <v>25.19773948123348</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3966328514150774</v>
+        <v>2.358928096152098</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>11.15783415264313</v>
+        <v>13.12012939738015</v>
       </c>
       <c r="S27" t="n">
-        <v>82.68317110383782</v>
+        <v>84.64546634857484</v>
       </c>
       <c r="T27" t="n">
-        <v>111.1647286948216</v>
+        <v>113.1270239395586</v>
       </c>
       <c r="U27" t="n">
-        <v>136.9413820809748</v>
+        <v>138.9036773257118</v>
       </c>
       <c r="V27" t="n">
-        <v>143.8005871494253</v>
+        <v>145.7628823941623</v>
       </c>
       <c r="W27" t="n">
-        <v>162.6949831609196</v>
+        <v>164.6572784056566</v>
       </c>
       <c r="X27" t="n">
-        <v>116.7729852034775</v>
+        <v>118.7352804482145</v>
       </c>
       <c r="Y27" t="n">
-        <v>116.6826957773044</v>
+        <v>118.6449910220414</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90.8319801819373</v>
+        <v>92.79427542667432</v>
       </c>
       <c r="C28" t="n">
-        <v>78.24682109862783</v>
+        <v>80.20911634336485</v>
       </c>
       <c r="D28" t="n">
-        <v>59.61547301821236</v>
+        <v>61.57776826294938</v>
       </c>
       <c r="E28" t="n">
-        <v>57.43396264656917</v>
+        <v>59.39625789130619</v>
       </c>
       <c r="F28" t="n">
-        <v>56.42104802293125</v>
+        <v>58.38334326766827</v>
       </c>
       <c r="G28" t="n">
-        <v>78.99097935845876</v>
+        <v>80.95327460319578</v>
       </c>
       <c r="H28" t="n">
-        <v>73.22717250743958</v>
+        <v>75.1894677521766</v>
       </c>
       <c r="I28" t="n">
-        <v>66.45047492725828</v>
+        <v>68.41277017199531</v>
       </c>
       <c r="J28" t="n">
-        <v>4.359180116672775</v>
+        <v>6.321475361409796</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>88.29339137716948</v>
+        <v>90.25568662190651</v>
       </c>
       <c r="S28" t="n">
-        <v>135.0165980369723</v>
+        <v>136.9788932817093</v>
       </c>
       <c r="T28" t="n">
-        <v>138.9455894282815</v>
+        <v>140.9078846730185</v>
       </c>
       <c r="U28" t="n">
-        <v>197.3190293564909</v>
+        <v>199.2813246012279</v>
       </c>
       <c r="V28" t="n">
-        <v>163.137643323828</v>
+        <v>165.099938568565</v>
       </c>
       <c r="W28" t="n">
-        <v>197.522998336591</v>
+        <v>199.485293581328</v>
       </c>
       <c r="X28" t="n">
-        <v>136.7096553890372</v>
+        <v>138.6719506337742</v>
       </c>
       <c r="Y28" t="n">
-        <v>129.5846533520948</v>
+        <v>131.5469485968318</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>238.7338416634806</v>
+        <v>237.6646292700967</v>
       </c>
       <c r="C29" t="n">
-        <v>221.2728917710076</v>
+        <v>220.2036793776237</v>
       </c>
       <c r="D29" t="n">
-        <v>210.683041620683</v>
+        <v>209.6138292272991</v>
       </c>
       <c r="E29" t="n">
-        <v>237.9303700722618</v>
+        <v>236.8611576788779</v>
       </c>
       <c r="F29" t="n">
-        <v>262.8760457417114</v>
+        <v>261.8068333483276</v>
       </c>
       <c r="G29" t="n">
-        <v>271.302737515135</v>
+        <v>270.2335251217512</v>
       </c>
       <c r="H29" t="n">
-        <v>195.4748021157671</v>
+        <v>194.4055897223833</v>
       </c>
       <c r="I29" t="n">
-        <v>66.47588957040591</v>
+        <v>65.40667717702203</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5.869117941149682</v>
+        <v>4.799905547765803</v>
       </c>
       <c r="S29" t="n">
-        <v>65.02006958624534</v>
+        <v>63.95085719286146</v>
       </c>
       <c r="T29" t="n">
-        <v>79.09584956413136</v>
+        <v>78.02663717074748</v>
       </c>
       <c r="U29" t="n">
-        <v>107.3456529078365</v>
+        <v>106.2764405144526</v>
       </c>
       <c r="V29" t="n">
-        <v>183.7522584701349</v>
+        <v>182.683046076751</v>
       </c>
       <c r="W29" t="n">
-        <v>205.240968717413</v>
+        <v>204.1717563240291</v>
       </c>
       <c r="X29" t="n">
-        <v>225.731100678469</v>
+        <v>224.6618882850852</v>
       </c>
       <c r="Y29" t="n">
-        <v>242.2379386560536</v>
+        <v>241.1687262626697</v>
       </c>
     </row>
     <row r="30">
@@ -24716,19 +24716,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.53318364986734</v>
+        <v>21.46397125648346</v>
       </c>
       <c r="C30" t="n">
-        <v>28.70849898831574</v>
+        <v>27.63928659493186</v>
       </c>
       <c r="D30" t="n">
-        <v>3.445065564638753</v>
+        <v>2.375853171254874</v>
       </c>
       <c r="E30" t="n">
-        <v>13.64508045540094</v>
+        <v>12.57586806201707</v>
       </c>
       <c r="F30" t="n">
-        <v>1.069212393383879</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>27.68317110383782</v>
+        <v>26.61395871045394</v>
       </c>
       <c r="T30" t="n">
-        <v>56.1647286948216</v>
+        <v>55.09551630143773</v>
       </c>
       <c r="U30" t="n">
-        <v>81.94138208097482</v>
+        <v>80.87216968759094</v>
       </c>
       <c r="V30" t="n">
-        <v>88.80058714942527</v>
+        <v>87.73137475604139</v>
       </c>
       <c r="W30" t="n">
-        <v>107.6949831609196</v>
+        <v>106.6257707675357</v>
       </c>
       <c r="X30" t="n">
-        <v>61.77298520347748</v>
+        <v>60.7037728100936</v>
       </c>
       <c r="Y30" t="n">
-        <v>61.68269577730436</v>
+        <v>60.61348338392048</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35.8319801819373</v>
+        <v>34.76276778855342</v>
       </c>
       <c r="C31" t="n">
-        <v>23.24682109862783</v>
+        <v>22.17760870524396</v>
       </c>
       <c r="D31" t="n">
-        <v>4.615473018212356</v>
+        <v>3.546260624828477</v>
       </c>
       <c r="E31" t="n">
-        <v>2.433962646569171</v>
+        <v>1.364750253185292</v>
       </c>
       <c r="F31" t="n">
-        <v>1.421048022931245</v>
+        <v>0.3518356295473666</v>
       </c>
       <c r="G31" t="n">
-        <v>23.99097935845876</v>
+        <v>22.92176696507488</v>
       </c>
       <c r="H31" t="n">
-        <v>18.22717250743958</v>
+        <v>17.1579601140557</v>
       </c>
       <c r="I31" t="n">
-        <v>11.45047492725828</v>
+        <v>10.38126253387441</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>33.29339137716948</v>
+        <v>32.22417898378561</v>
       </c>
       <c r="S31" t="n">
-        <v>80.01659803697225</v>
+        <v>78.94738564358838</v>
       </c>
       <c r="T31" t="n">
-        <v>83.94558942828149</v>
+        <v>82.87637703489762</v>
       </c>
       <c r="U31" t="n">
-        <v>142.3190293564909</v>
+        <v>141.249816963107</v>
       </c>
       <c r="V31" t="n">
-        <v>108.137643323828</v>
+        <v>107.0684309304441</v>
       </c>
       <c r="W31" t="n">
-        <v>142.522998336591</v>
+        <v>141.4537859432071</v>
       </c>
       <c r="X31" t="n">
-        <v>81.70965538903715</v>
+        <v>80.64044299565327</v>
       </c>
       <c r="Y31" t="n">
-        <v>74.58465335209479</v>
+        <v>73.51544095871091</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>238.7338416634806</v>
+        <v>237.6646292700967</v>
       </c>
       <c r="C32" t="n">
-        <v>221.2728917710076</v>
+        <v>220.2036793776237</v>
       </c>
       <c r="D32" t="n">
-        <v>210.683041620683</v>
+        <v>209.6138292272991</v>
       </c>
       <c r="E32" t="n">
-        <v>237.9303700722618</v>
+        <v>236.8611576788779</v>
       </c>
       <c r="F32" t="n">
-        <v>262.8760457417114</v>
+        <v>261.8068333483276</v>
       </c>
       <c r="G32" t="n">
-        <v>271.302737515135</v>
+        <v>270.2335251217512</v>
       </c>
       <c r="H32" t="n">
-        <v>195.4748021157671</v>
+        <v>194.4055897223833</v>
       </c>
       <c r="I32" t="n">
-        <v>66.47588957040591</v>
+        <v>65.40667717702203</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>5.869117941149682</v>
+        <v>4.799905547765803</v>
       </c>
       <c r="S32" t="n">
-        <v>65.02006958624534</v>
+        <v>63.95085719286146</v>
       </c>
       <c r="T32" t="n">
-        <v>79.09584956413136</v>
+        <v>78.02663717074748</v>
       </c>
       <c r="U32" t="n">
-        <v>107.3456529078365</v>
+        <v>106.2764405144526</v>
       </c>
       <c r="V32" t="n">
-        <v>183.7522584701349</v>
+        <v>182.683046076751</v>
       </c>
       <c r="W32" t="n">
-        <v>205.240968717413</v>
+        <v>204.1717563240291</v>
       </c>
       <c r="X32" t="n">
-        <v>225.731100678469</v>
+        <v>224.6618882850852</v>
       </c>
       <c r="Y32" t="n">
-        <v>242.2379386560536</v>
+        <v>241.1687262626697</v>
       </c>
     </row>
     <row r="33">
@@ -24953,19 +24953,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.53318364986734</v>
+        <v>21.46397125648346</v>
       </c>
       <c r="C33" t="n">
-        <v>28.70849898831574</v>
+        <v>27.63928659493186</v>
       </c>
       <c r="D33" t="n">
-        <v>3.445065564638753</v>
+        <v>2.375853171254874</v>
       </c>
       <c r="E33" t="n">
-        <v>13.64508045540094</v>
+        <v>12.57586806201707</v>
       </c>
       <c r="F33" t="n">
-        <v>1.069212393383879</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>27.68317110383782</v>
+        <v>26.61395871045394</v>
       </c>
       <c r="T33" t="n">
-        <v>56.1647286948216</v>
+        <v>55.09551630143773</v>
       </c>
       <c r="U33" t="n">
-        <v>81.94138208097482</v>
+        <v>80.87216968759094</v>
       </c>
       <c r="V33" t="n">
-        <v>88.80058714942527</v>
+        <v>87.73137475604139</v>
       </c>
       <c r="W33" t="n">
-        <v>107.6949831609196</v>
+        <v>106.6257707675357</v>
       </c>
       <c r="X33" t="n">
-        <v>61.77298520347748</v>
+        <v>60.7037728100936</v>
       </c>
       <c r="Y33" t="n">
-        <v>61.68269577730436</v>
+        <v>60.61348338392048</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>35.8319801819373</v>
+        <v>34.76276778855342</v>
       </c>
       <c r="C34" t="n">
-        <v>23.24682109862783</v>
+        <v>22.17760870524396</v>
       </c>
       <c r="D34" t="n">
-        <v>4.615473018212356</v>
+        <v>3.546260624828477</v>
       </c>
       <c r="E34" t="n">
-        <v>2.433962646569171</v>
+        <v>1.364750253185292</v>
       </c>
       <c r="F34" t="n">
-        <v>1.421048022931245</v>
+        <v>0.3518356295473666</v>
       </c>
       <c r="G34" t="n">
-        <v>23.99097935845876</v>
+        <v>22.92176696507488</v>
       </c>
       <c r="H34" t="n">
-        <v>18.22717250743958</v>
+        <v>17.1579601140557</v>
       </c>
       <c r="I34" t="n">
-        <v>11.45047492725828</v>
+        <v>10.38126253387441</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>33.29339137716948</v>
+        <v>32.22417898378561</v>
       </c>
       <c r="S34" t="n">
-        <v>80.01659803697225</v>
+        <v>78.94738564358838</v>
       </c>
       <c r="T34" t="n">
-        <v>83.94558942828149</v>
+        <v>82.87637703489762</v>
       </c>
       <c r="U34" t="n">
-        <v>142.3190293564909</v>
+        <v>141.249816963107</v>
       </c>
       <c r="V34" t="n">
-        <v>108.137643323828</v>
+        <v>107.0684309304441</v>
       </c>
       <c r="W34" t="n">
-        <v>142.522998336591</v>
+        <v>141.4537859432071</v>
       </c>
       <c r="X34" t="n">
-        <v>81.70965538903715</v>
+        <v>80.64044299565327</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.58465335209479</v>
+        <v>73.51544095871091</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>238.7338416634806</v>
+        <v>237.6646292700967</v>
       </c>
       <c r="C35" t="n">
-        <v>221.2728917710076</v>
+        <v>220.2036793776237</v>
       </c>
       <c r="D35" t="n">
-        <v>210.683041620683</v>
+        <v>209.6138292272991</v>
       </c>
       <c r="E35" t="n">
-        <v>237.9303700722618</v>
+        <v>236.8611576788779</v>
       </c>
       <c r="F35" t="n">
-        <v>262.8760457417114</v>
+        <v>261.8068333483276</v>
       </c>
       <c r="G35" t="n">
-        <v>271.302737515135</v>
+        <v>270.2335251217512</v>
       </c>
       <c r="H35" t="n">
-        <v>195.4748021157671</v>
+        <v>194.4055897223833</v>
       </c>
       <c r="I35" t="n">
-        <v>66.47588957040591</v>
+        <v>65.40667717702203</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>5.869117941149682</v>
+        <v>4.799905547765803</v>
       </c>
       <c r="S35" t="n">
-        <v>65.02006958624534</v>
+        <v>63.95085719286146</v>
       </c>
       <c r="T35" t="n">
-        <v>79.09584956413136</v>
+        <v>78.02663717074748</v>
       </c>
       <c r="U35" t="n">
-        <v>107.3456529078365</v>
+        <v>106.2764405144526</v>
       </c>
       <c r="V35" t="n">
-        <v>183.7522584701349</v>
+        <v>182.683046076751</v>
       </c>
       <c r="W35" t="n">
-        <v>205.240968717413</v>
+        <v>204.1717563240291</v>
       </c>
       <c r="X35" t="n">
-        <v>225.731100678469</v>
+        <v>224.6618882850852</v>
       </c>
       <c r="Y35" t="n">
-        <v>242.2379386560536</v>
+        <v>241.1687262626697</v>
       </c>
     </row>
     <row r="36">
@@ -25190,19 +25190,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>22.53318364986734</v>
+        <v>21.46397125648346</v>
       </c>
       <c r="C36" t="n">
-        <v>28.70849898831574</v>
+        <v>27.63928659493186</v>
       </c>
       <c r="D36" t="n">
-        <v>3.445065564638753</v>
+        <v>2.375853171254874</v>
       </c>
       <c r="E36" t="n">
-        <v>13.64508045540094</v>
+        <v>12.57586806201707</v>
       </c>
       <c r="F36" t="n">
-        <v>1.069212393383879</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>27.68317110383782</v>
+        <v>26.61395871045394</v>
       </c>
       <c r="T36" t="n">
-        <v>56.1647286948216</v>
+        <v>55.09551630143773</v>
       </c>
       <c r="U36" t="n">
-        <v>81.94138208097482</v>
+        <v>80.87216968759094</v>
       </c>
       <c r="V36" t="n">
-        <v>88.80058714942527</v>
+        <v>87.73137475604139</v>
       </c>
       <c r="W36" t="n">
-        <v>107.6949831609196</v>
+        <v>106.6257707675357</v>
       </c>
       <c r="X36" t="n">
-        <v>61.77298520347748</v>
+        <v>60.7037728100936</v>
       </c>
       <c r="Y36" t="n">
-        <v>61.68269577730436</v>
+        <v>60.61348338392048</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>35.8319801819373</v>
+        <v>34.76276778855342</v>
       </c>
       <c r="C37" t="n">
-        <v>23.24682109862783</v>
+        <v>22.17760870524396</v>
       </c>
       <c r="D37" t="n">
-        <v>4.615473018212356</v>
+        <v>3.546260624828477</v>
       </c>
       <c r="E37" t="n">
-        <v>2.433962646569171</v>
+        <v>1.364750253185292</v>
       </c>
       <c r="F37" t="n">
-        <v>1.421048022931245</v>
+        <v>0.3518356295473666</v>
       </c>
       <c r="G37" t="n">
-        <v>23.99097935845876</v>
+        <v>22.92176696507488</v>
       </c>
       <c r="H37" t="n">
-        <v>18.22717250743958</v>
+        <v>17.1579601140557</v>
       </c>
       <c r="I37" t="n">
-        <v>11.45047492725828</v>
+        <v>10.38126253387441</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>33.29339137716948</v>
+        <v>32.22417898378561</v>
       </c>
       <c r="S37" t="n">
-        <v>80.01659803697225</v>
+        <v>78.94738564358838</v>
       </c>
       <c r="T37" t="n">
-        <v>83.94558942828149</v>
+        <v>82.87637703489762</v>
       </c>
       <c r="U37" t="n">
-        <v>142.3190293564909</v>
+        <v>141.249816963107</v>
       </c>
       <c r="V37" t="n">
-        <v>108.137643323828</v>
+        <v>107.0684309304441</v>
       </c>
       <c r="W37" t="n">
-        <v>142.522998336591</v>
+        <v>141.4537859432071</v>
       </c>
       <c r="X37" t="n">
-        <v>81.70965538903715</v>
+        <v>80.64044299565327</v>
       </c>
       <c r="Y37" t="n">
-        <v>74.58465335209479</v>
+        <v>73.51544095871091</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>238.7338416634806</v>
+        <v>237.6646292700967</v>
       </c>
       <c r="C38" t="n">
-        <v>221.2728917710076</v>
+        <v>220.2036793776237</v>
       </c>
       <c r="D38" t="n">
-        <v>210.683041620683</v>
+        <v>209.6138292272991</v>
       </c>
       <c r="E38" t="n">
-        <v>237.9303700722618</v>
+        <v>236.8611576788779</v>
       </c>
       <c r="F38" t="n">
-        <v>262.8760457417114</v>
+        <v>261.8068333483276</v>
       </c>
       <c r="G38" t="n">
-        <v>271.302737515135</v>
+        <v>270.2335251217512</v>
       </c>
       <c r="H38" t="n">
-        <v>195.4748021157671</v>
+        <v>194.4055897223833</v>
       </c>
       <c r="I38" t="n">
-        <v>66.47588957040591</v>
+        <v>65.40667717702203</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>5.869117941149682</v>
+        <v>4.799905547765803</v>
       </c>
       <c r="S38" t="n">
-        <v>65.02006958624534</v>
+        <v>63.95085719286146</v>
       </c>
       <c r="T38" t="n">
-        <v>79.09584956413136</v>
+        <v>78.02663717074748</v>
       </c>
       <c r="U38" t="n">
-        <v>107.3456529078365</v>
+        <v>106.2764405144526</v>
       </c>
       <c r="V38" t="n">
-        <v>183.7522584701349</v>
+        <v>182.683046076751</v>
       </c>
       <c r="W38" t="n">
-        <v>205.240968717413</v>
+        <v>204.1717563240291</v>
       </c>
       <c r="X38" t="n">
-        <v>225.731100678469</v>
+        <v>224.6618882850852</v>
       </c>
       <c r="Y38" t="n">
-        <v>242.2379386560536</v>
+        <v>241.1687262626697</v>
       </c>
     </row>
     <row r="39">
@@ -25427,19 +25427,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22.53318364986734</v>
+        <v>21.46397125648346</v>
       </c>
       <c r="C39" t="n">
-        <v>28.70849898831574</v>
+        <v>27.63928659493186</v>
       </c>
       <c r="D39" t="n">
-        <v>3.445065564638753</v>
+        <v>2.375853171254874</v>
       </c>
       <c r="E39" t="n">
-        <v>13.64508045540094</v>
+        <v>12.57586806201707</v>
       </c>
       <c r="F39" t="n">
-        <v>1.069212393383879</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>27.68317110383782</v>
+        <v>26.61395871045394</v>
       </c>
       <c r="T39" t="n">
-        <v>56.1647286948216</v>
+        <v>55.09551630143773</v>
       </c>
       <c r="U39" t="n">
-        <v>81.94138208097482</v>
+        <v>80.87216968759094</v>
       </c>
       <c r="V39" t="n">
-        <v>88.80058714942527</v>
+        <v>87.73137475604139</v>
       </c>
       <c r="W39" t="n">
-        <v>107.6949831609196</v>
+        <v>106.6257707675357</v>
       </c>
       <c r="X39" t="n">
-        <v>61.77298520347748</v>
+        <v>60.7037728100936</v>
       </c>
       <c r="Y39" t="n">
-        <v>61.68269577730436</v>
+        <v>60.61348338392048</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>35.8319801819373</v>
+        <v>34.76276778855342</v>
       </c>
       <c r="C40" t="n">
-        <v>23.24682109862783</v>
+        <v>22.17760870524396</v>
       </c>
       <c r="D40" t="n">
-        <v>4.615473018212356</v>
+        <v>3.546260624828477</v>
       </c>
       <c r="E40" t="n">
-        <v>2.433962646569171</v>
+        <v>1.364750253185292</v>
       </c>
       <c r="F40" t="n">
-        <v>1.421048022931245</v>
+        <v>0.3518356295473666</v>
       </c>
       <c r="G40" t="n">
-        <v>23.99097935845876</v>
+        <v>22.92176696507488</v>
       </c>
       <c r="H40" t="n">
-        <v>18.22717250743958</v>
+        <v>17.1579601140557</v>
       </c>
       <c r="I40" t="n">
-        <v>11.45047492725828</v>
+        <v>10.38126253387441</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>33.29339137716948</v>
+        <v>32.22417898378561</v>
       </c>
       <c r="S40" t="n">
-        <v>80.01659803697225</v>
+        <v>78.94738564358838</v>
       </c>
       <c r="T40" t="n">
-        <v>83.94558942828149</v>
+        <v>82.87637703489762</v>
       </c>
       <c r="U40" t="n">
-        <v>142.3190293564909</v>
+        <v>141.249816963107</v>
       </c>
       <c r="V40" t="n">
-        <v>108.137643323828</v>
+        <v>107.0684309304441</v>
       </c>
       <c r="W40" t="n">
-        <v>142.522998336591</v>
+        <v>141.4537859432071</v>
       </c>
       <c r="X40" t="n">
-        <v>81.70965538903715</v>
+        <v>80.64044299565327</v>
       </c>
       <c r="Y40" t="n">
-        <v>74.58465335209479</v>
+        <v>73.51544095871091</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>246.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C41" t="n">
-        <v>229.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D41" t="n">
-        <v>218.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E41" t="n">
-        <v>245.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F41" t="n">
-        <v>270.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G41" t="n">
-        <v>279.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H41" t="n">
-        <v>203.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I41" t="n">
-        <v>74.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>13.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S41" t="n">
-        <v>73.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T41" t="n">
-        <v>87.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U41" t="n">
-        <v>115.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V41" t="n">
-        <v>191.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W41" t="n">
-        <v>213.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X41" t="n">
-        <v>233.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y41" t="n">
-        <v>250.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C42" t="n">
-        <v>36.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D42" t="n">
-        <v>11.44506556463875</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E42" t="n">
-        <v>21.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F42" t="n">
-        <v>9.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G42" t="n">
-        <v>1.343517163210635</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>35.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T42" t="n">
-        <v>64.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U42" t="n">
-        <v>89.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V42" t="n">
-        <v>96.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W42" t="n">
-        <v>115.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X42" t="n">
-        <v>69.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y42" t="n">
-        <v>69.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>43.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C43" t="n">
-        <v>31.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D43" t="n">
-        <v>12.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E43" t="n">
-        <v>10.43396264656917</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F43" t="n">
-        <v>9.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G43" t="n">
-        <v>31.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H43" t="n">
-        <v>26.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I43" t="n">
-        <v>19.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>41.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S43" t="n">
-        <v>88.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T43" t="n">
-        <v>91.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U43" t="n">
-        <v>150.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V43" t="n">
-        <v>116.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W43" t="n">
-        <v>150.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X43" t="n">
-        <v>89.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y43" t="n">
-        <v>82.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>320369.2162084327</v>
+        <v>322435.4868791294</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>489418.8115243776</v>
+        <v>487920.7995225257</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>489418.8115243776</v>
+        <v>487920.7995225257</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>489418.8115243776</v>
+        <v>487920.7995225257</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>489418.8115243776</v>
+        <v>487920.7995225257</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>483320.3964455901</v>
+        <v>479268.256765208</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>590754.1894218201</v>
+        <v>592780.9884347185</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>590754.1894218201</v>
+        <v>592780.9884347185</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>590754.1894218201</v>
+        <v>592780.9884347185</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>590754.1894218201</v>
+        <v>592780.9884347185</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>575539.544935065</v>
+        <v>578136.1605564022</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>716866.7963774089</v>
+        <v>716866.7963774088</v>
       </c>
       <c r="C2" t="n">
+        <v>716866.7963774088</v>
+      </c>
+      <c r="D2" t="n">
         <v>716866.7963774087</v>
       </c>
-      <c r="D2" t="n">
-        <v>716866.7963774084</v>
-      </c>
       <c r="E2" t="n">
-        <v>212861.8106739656</v>
+        <v>214928.0813476831</v>
       </c>
       <c r="F2" t="n">
-        <v>381911.405992931</v>
+        <v>380413.3939910796</v>
       </c>
       <c r="G2" t="n">
-        <v>381911.405992931</v>
+        <v>380413.3939910795</v>
       </c>
       <c r="H2" t="n">
-        <v>381911.405992931</v>
+        <v>380413.3939910792</v>
       </c>
       <c r="I2" t="n">
-        <v>381911.405992931</v>
+        <v>380413.3939910784</v>
       </c>
       <c r="J2" t="n">
-        <v>375812.9909141436</v>
+        <v>371760.8512337616</v>
       </c>
       <c r="K2" t="n">
-        <v>483246.7838903734</v>
+        <v>485273.5829032721</v>
       </c>
       <c r="L2" t="n">
-        <v>483246.7838903734</v>
+        <v>485273.582903272</v>
       </c>
       <c r="M2" t="n">
-        <v>483246.7838903734</v>
+        <v>485273.5829032721</v>
       </c>
       <c r="N2" t="n">
-        <v>483246.7838903732</v>
+        <v>485273.5829032722</v>
       </c>
       <c r="O2" t="n">
-        <v>468032.1394036183</v>
+        <v>470628.7550249557</v>
       </c>
       <c r="P2" t="n">
         <v>188137.9596800312</v>
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8800</v>
+        <v>9559.431483690014</v>
       </c>
       <c r="F3" t="n">
-        <v>64800</v>
+        <v>63449.60762007179</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6400</v>
+        <v>6180.556184138595</v>
       </c>
       <c r="K3" t="n">
-        <v>108800</v>
+        <v>109874.8137305685</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="C4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="D4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="E4" t="n">
-        <v>123634.9028209154</v>
+        <v>124455.3967726702</v>
       </c>
       <c r="F4" t="n">
-        <v>233906.8378454829</v>
+        <v>232402.3315691932</v>
       </c>
       <c r="G4" t="n">
-        <v>233906.8378454829</v>
+        <v>232402.3315691932</v>
       </c>
       <c r="H4" t="n">
-        <v>233906.8378454829</v>
+        <v>232402.3315691932</v>
       </c>
       <c r="I4" t="n">
-        <v>233906.8378454829</v>
+        <v>232402.3315691932</v>
       </c>
       <c r="J4" t="n">
-        <v>229928.809799631</v>
+        <v>226758.2326825385</v>
       </c>
       <c r="K4" t="n">
-        <v>300008.4347530484</v>
+        <v>300803.1811336951</v>
       </c>
       <c r="L4" t="n">
-        <v>300008.4347530484</v>
+        <v>300803.1811336952</v>
       </c>
       <c r="M4" t="n">
-        <v>300008.4347530484</v>
+        <v>300803.1811336951</v>
       </c>
       <c r="N4" t="n">
-        <v>300008.4347530484</v>
+        <v>300803.1811336952</v>
       </c>
       <c r="O4" t="n">
-        <v>290083.8425936028</v>
+        <v>291250.2833276311</v>
       </c>
       <c r="P4" t="n">
-        <v>107507.4055314464</v>
+        <v>106980.0603174001</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>924.759</v>
+        <v>1004.56480675292</v>
       </c>
       <c r="F5" t="n">
-        <v>7734.348</v>
+        <v>7672.246135517689</v>
       </c>
       <c r="G5" t="n">
-        <v>7734.348</v>
+        <v>7672.246135517689</v>
       </c>
       <c r="H5" t="n">
-        <v>7734.348</v>
+        <v>7672.246135517689</v>
       </c>
       <c r="I5" t="n">
-        <v>7734.348</v>
+        <v>7672.246135517689</v>
       </c>
       <c r="J5" t="n">
-        <v>7482.141000000001</v>
+        <v>7317.172801070204</v>
       </c>
       <c r="K5" t="n">
-        <v>12105.936</v>
+        <v>12195.82361669939</v>
       </c>
       <c r="L5" t="n">
-        <v>12105.936</v>
+        <v>12195.82361669939</v>
       </c>
       <c r="M5" t="n">
-        <v>12105.936</v>
+        <v>12195.82361669939</v>
       </c>
       <c r="N5" t="n">
-        <v>12105.936</v>
+        <v>12195.82361669939</v>
       </c>
       <c r="O5" t="n">
-        <v>11433.384</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>230839.2058284437</v>
+        <v>231366.55104249</v>
       </c>
       <c r="C6" t="n">
-        <v>230839.2058284435</v>
+        <v>231366.55104249</v>
       </c>
       <c r="D6" t="n">
-        <v>230839.2058284433</v>
+        <v>231366.5510424899</v>
       </c>
       <c r="E6" t="n">
-        <v>79502.14885305021</v>
+        <v>79908.68828456996</v>
       </c>
       <c r="F6" t="n">
-        <v>75470.22014744816</v>
+        <v>76889.208666297</v>
       </c>
       <c r="G6" t="n">
-        <v>140270.2201474481</v>
+        <v>140338.8162863687</v>
       </c>
       <c r="H6" t="n">
-        <v>140270.2201474481</v>
+        <v>140338.8162863684</v>
       </c>
       <c r="I6" t="n">
-        <v>140270.2201474481</v>
+        <v>140338.8162863676</v>
       </c>
       <c r="J6" t="n">
-        <v>132002.0401145126</v>
+        <v>131504.8895660144</v>
       </c>
       <c r="K6" t="n">
-        <v>62332.41313732507</v>
+        <v>62399.76442230905</v>
       </c>
       <c r="L6" t="n">
-        <v>171132.4131373251</v>
+        <v>172274.5781528774</v>
       </c>
       <c r="M6" t="n">
-        <v>171132.4131373251</v>
+        <v>172274.5781528776</v>
       </c>
       <c r="N6" t="n">
-        <v>171132.4131373249</v>
+        <v>172274.5781528776</v>
       </c>
       <c r="O6" t="n">
-        <v>166514.9128100155</v>
+        <v>167832.1395529306</v>
       </c>
       <c r="P6" t="n">
-        <v>80630.55414858476</v>
+        <v>81157.89936263111</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G2" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H2" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I2" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J2" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="K2" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="L2" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="M2" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="N2" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="O2" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26840,19 +26840,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>79.31200952508974</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -26861,28 +26861,28 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="K2" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K2" t="n">
-        <v>81</v>
+        <v>79.31200952508974</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="P2" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="3">
@@ -28012,31 +28012,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -28060,28 +28060,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="12">
@@ -28091,31 +28091,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465911866208053</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="13">
@@ -28170,34 +28170,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -28215,31 +28215,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="R13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="14">
@@ -28249,28 +28249,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -28297,28 +28297,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y14" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="15">
@@ -28328,25 +28328,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -28376,28 +28376,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y15" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="16">
@@ -28407,31 +28407,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -28455,28 +28455,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y16" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="17">
@@ -28486,28 +28486,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -28534,28 +28534,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y17" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="18">
@@ -28565,25 +28565,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -28613,28 +28613,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y18" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="19">
@@ -28644,31 +28644,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="K19" t="n">
         <v>22.26949182588285</v>
@@ -28692,28 +28692,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y19" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="20">
@@ -28723,28 +28723,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -28771,28 +28771,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y20" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="21">
@@ -28802,25 +28802,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -28850,28 +28850,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y21" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="22">
@@ -28881,31 +28881,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="K22" t="n">
         <v>22.26949182588285</v>
@@ -28929,28 +28929,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y22" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="23">
@@ -28960,28 +28960,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -29008,28 +29008,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y23" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="24">
@@ -29039,25 +29039,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y24" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="25">
@@ -29118,31 +29118,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="K25" t="n">
         <v>22.26949182588285</v>
@@ -29166,28 +29166,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y25" t="n">
-        <v>92</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="26">
@@ -29197,28 +29197,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="C26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="D26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="E26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="F26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="G26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="H26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="I26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -29245,28 +29245,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="S26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="T26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="U26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="V26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="W26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="X26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="Y26" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
     </row>
     <row r="27">
@@ -29276,28 +29276,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="C27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="D27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="E27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="F27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="G27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="H27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="I27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="S27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="T27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="U27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="V27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="W27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="X27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="Y27" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
     </row>
     <row r="28">
@@ -29355,31 +29355,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="C28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="D28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="E28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="F28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="G28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="H28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="I28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="J28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="K28" t="n">
         <v>22.26949182588285</v>
@@ -29403,28 +29403,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="S28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="T28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="U28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="V28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="W28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="X28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="Y28" t="n">
-        <v>89</v>
+        <v>87.03770475526298</v>
       </c>
     </row>
     <row r="29">
@@ -29434,28 +29434,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -29482,28 +29482,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y29" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="30">
@@ -29513,19 +29513,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
         <v>137.3435171632106</v>
@@ -29564,25 +29564,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y30" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -29640,28 +29640,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y31" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="32">
@@ -29671,28 +29671,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -29719,28 +29719,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y32" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="33">
@@ -29750,19 +29750,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
         <v>137.3435171632106</v>
@@ -29801,25 +29801,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y33" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J34" t="n">
         <v>93.35918011667277</v>
@@ -29877,28 +29877,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y34" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="35">
@@ -29908,28 +29908,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -29956,28 +29956,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y35" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="36">
@@ -29987,19 +29987,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -30038,25 +30038,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y36" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -30114,28 +30114,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y37" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="38">
@@ -30145,28 +30145,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -30193,28 +30193,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y38" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="39">
@@ -30224,19 +30224,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
@@ -30275,25 +30275,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y39" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
@@ -30351,28 +30351,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y40" t="n">
-        <v>144</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="41">
@@ -30382,28 +30382,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -30430,28 +30430,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y41" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="42">
@@ -30461,22 +30461,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -30512,25 +30512,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y42" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="43">
@@ -30540,28 +30540,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -30588,28 +30588,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y43" t="n">
-        <v>136</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="44">
@@ -35410,7 +35410,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.424722492773959e-07</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
